--- a/MEME_OUTPUT/reverse_meme_out_1_motif5.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_1_motif5.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.5426</v>
+        <v>0.5425829668132747</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.136</v>
+        <v>0.1361455417832867</v>
       </c>
     </row>
     <row r="4">
@@ -535,16 +535,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>0.3646</v>
+        <v>0.3646541383446621</v>
       </c>
     </row>
     <row r="5">
@@ -564,16 +564,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9984</v>
+        <v>0.9982007197121151</v>
       </c>
     </row>
     <row r="6">
@@ -598,11 +598,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.9998</v>
+        <v>0.9996001599360256</v>
       </c>
     </row>
     <row r="7">
@@ -622,16 +622,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.9764</v>
+        <v>0.9762095161935226</v>
       </c>
     </row>
     <row r="8">
@@ -651,16 +651,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9852059176329468</v>
       </c>
     </row>
     <row r="9">
@@ -680,16 +680,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.9986</v>
+        <v>0.9984006397441023</v>
       </c>
     </row>
     <row r="10">
@@ -709,16 +709,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.9806</v>
+        <v>0.9804078368652539</v>
       </c>
     </row>
     <row r="11">
@@ -738,16 +738,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.992203118752499</v>
       </c>
     </row>
     <row r="12">
@@ -767,16 +767,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.999</v>
+        <v>0.9988004798080767</v>
       </c>
     </row>
     <row r="13">
@@ -796,16 +796,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.9596</v>
+        <v>0.9594162335065973</v>
       </c>
     </row>
     <row r="14">
@@ -825,16 +825,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.757</v>
+        <v>0.7568972411035586</v>
       </c>
     </row>
     <row r="15">
@@ -854,16 +854,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.9596</v>
+        <v>0.9594162335065973</v>
       </c>
     </row>
     <row r="16">
@@ -883,16 +883,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.9906</v>
+        <v>0.9904038384646141</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/reverse_meme_out_1_motif5.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_1_motif5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>AAAATTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.5425829668132747</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>AAAATTTGTTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;ATTTG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.1361455417832867</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AAATTTGTTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TTTG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.3646541383446621</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>AAAGTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9982007197121151</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>ATAT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9996001599360256</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>TTATATGAA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;ATATG&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9762095161935226</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>TTATATGAAA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;ATATGA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9852059176329468</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TTATATGAAAA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;ATATGAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9984006397441023</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>AAAATT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AA&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9804078368652539</v>
       </c>
     </row>
@@ -738,15 +838,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>AAATTT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.992203118752499</v>
       </c>
     </row>
@@ -767,15 +877,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>AATTT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.9988004798080767</v>
       </c>
     </row>
@@ -796,15 +916,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>AAAGTTATATGAAAATTTGTT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AGTTATATGAAAATTTG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.9594162335065973</v>
       </c>
     </row>
@@ -825,15 +955,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>AAAATTTGTT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AATTTG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.7568972411035586</v>
       </c>
     </row>
@@ -854,15 +994,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>AAAGTTATATGAAAATTTGTTT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AGTTATATGAAAATTTGT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.9594162335065973</v>
       </c>
     </row>
@@ -883,15 +1033,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>AATTTGTTT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TTTGT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.9904038384646141</v>
       </c>
     </row>
